--- a/arista_territory3_chart.xlsx
+++ b/arista_territory3_chart.xlsx
@@ -8,27 +8,40 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/tarista_my_yearupunited_org/Documents/Documents/DATA_Labs/Capstone_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="548" documentId="8_{9846D487-E9F8-401F-A6B0-DD507E4A38D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C1AABED-D27D-47A7-B9A5-C2D46FF497AC}"/>
+  <xr:revisionPtr revIDLastSave="560" documentId="8_{9846D487-E9F8-401F-A6B0-DD507E4A38D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81D77117-13DA-4381-83D0-9625000F0D06}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="4" xr2:uid="{7FD76110-709A-4A48-B506-2929AD8376FE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{7FD76110-709A-4A48-B506-2929AD8376FE}"/>
   </bookViews>
   <sheets>
     <sheet name="avg_trans" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet5" sheetId="6" r:id="rId2"/>
     <sheet name="Sheet4" sheetId="5" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="10" r:id="rId5"/>
+    <sheet name="graph" sheetId="10" r:id="rId5"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">avg_trans!$A$1:$F$289</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="120" r:id="rId7"/>
-    <pivotCache cacheId="107" r:id="rId8"/>
-    <pivotCache cacheId="125" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
+    <pivotCache cacheId="3" r:id="rId8"/>
+    <pivotCache cacheId="4" r:id="rId9"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -735,7 +748,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -749,6 +762,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3067,24 +3081,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dash"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="70000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3140,24 +3137,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3213,24 +3193,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="80000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3286,24 +3249,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dash"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3359,24 +3305,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dot"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="70000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3432,20 +3361,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="star"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3501,24 +3417,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="80000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3574,24 +3473,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dot"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3647,20 +3529,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="plus"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3716,20 +3585,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="x"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3785,24 +3641,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="80000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3858,20 +3697,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="plus"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3927,26 +3753,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="70000"/>
-                <a:lumOff val="30000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4002,26 +3809,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4077,26 +3865,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dash"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="80000"/>
-                <a:lumOff val="20000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4152,20 +3921,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4221,21 +3977,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="star"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4291,26 +4033,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4366,26 +4089,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dot"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:lumMod val="80000"/>
-                <a:lumOff val="20000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4441,18 +4145,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="star"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4508,21 +4201,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="x"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4578,26 +4257,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4653,21 +4313,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="plus"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4723,18 +4369,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="x"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4790,26 +4425,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="70000"/>
-                <a:lumOff val="30000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4865,26 +4481,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dash"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4940,26 +4537,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="80000"/>
-                <a:lumOff val="20000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5015,20 +4593,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5084,26 +4649,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="70000"/>
-                <a:lumOff val="30000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5159,26 +4705,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dot"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5234,21 +4761,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="star"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5304,20 +4817,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5373,26 +4873,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:lumMod val="70000"/>
-                <a:lumOff val="30000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5448,21 +4929,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="plus"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5518,21 +4985,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="x"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5588,20 +5041,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5657,24 +5097,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="70000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5730,24 +5153,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dash"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5803,24 +5209,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="80000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5876,24 +5265,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="triangle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5949,24 +5321,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:lumMod val="70000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6022,24 +5377,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="dot"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:lumMod val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6095,20 +5433,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="star"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6164,24 +5489,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6237,24 +5545,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:lumMod val="70000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6310,20 +5601,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="plus"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6379,20 +5657,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="x"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -6448,24 +5713,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:lumMod val="60000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -12353,7 +11601,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[arista_territory3_chart.xlsx]Sheet2!PivotTable53</c:name>
+    <c:name>[arista_territory3_chart.xlsx]graph!PivotTable53</c:name>
     <c:fmtId val="14"/>
   </c:pivotSource>
   <c:chart>
@@ -12944,6 +12192,286 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -12965,7 +12493,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$B$3:$B$4</c:f>
+              <c:f>graph!$B$3:$B$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -12988,7 +12516,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet2!$A$5:$A$53</c:f>
+              <c:f>graph!$A$5:$A$53</c:f>
               <c:strCache>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
@@ -13140,7 +12668,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$B$5:$B$53</c:f>
+              <c:f>graph!$B$5:$B$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="48"/>
@@ -13303,7 +12831,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$C$3:$C$4</c:f>
+              <c:f>graph!$C$3:$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -13326,7 +12854,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet2!$A$5:$A$53</c:f>
+              <c:f>graph!$A$5:$A$53</c:f>
               <c:strCache>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
@@ -13478,7 +13006,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$C$5:$C$53</c:f>
+              <c:f>graph!$C$5:$C$53</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="48"/>
@@ -13887,8 +13415,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.87857825688791313"/>
           <c:y val="0.14415952201433854"/>
-          <c:w val="0.11336372538444782"/>
-          <c:h val="0.18190116413138385"/>
+          <c:w val="0.12142169398481888"/>
+          <c:h val="0.43882022603608556"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -20687,7 +20215,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5809F4A2-07C1-4709-9DC9-E64A572949A1}" name="PivotTable44" cacheId="107" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5809F4A2-07C1-4709-9DC9-E64A572949A1}" name="PivotTable44" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:D10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField numFmtId="16" showAll="0" defaultSubtotal="0">
@@ -20962,7 +20490,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A823535-2BD9-4780-9737-CC59FD9BDFBF}" name="PivotTable52" cacheId="120" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A823535-2BD9-4780-9737-CC59FD9BDFBF}" name="PivotTable52" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="10">
   <location ref="A106:AW109" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" compact="0" numFmtId="16" outline="0" showAll="0" defaultSubtotal="0">
@@ -22269,7 +21797,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FBC61E5-05BF-402A-BA9A-0513881DEB64}" name="PivotTable41" cacheId="120" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="21">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FBC61E5-05BF-402A-BA9A-0513881DEB64}" name="PivotTable41" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="21">
   <location ref="A4:AW7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" compact="0" numFmtId="16" outline="0" showAll="0" defaultSubtotal="0">
@@ -23576,7 +23104,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74664E59-B9F7-4C8C-916D-F1C827D2A50F}" name="PivotTable53" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{74664E59-B9F7-4C8C-916D-F1C827D2A50F}" name="PivotTable53" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="28">
   <location ref="A3:D53" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" showAll="0">
@@ -24212,7 +23740,7 @@
   <dataFields count="1">
     <dataField name="Average of avg_trans" fld="3" subtotal="average" baseField="7" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="7">
     <chartFormat chart="14" format="7" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="2">
@@ -24233,6 +23761,66 @@
           </reference>
           <reference field="1" count="1" selected="0">
             <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="11" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="14" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -33376,14 +32964,14 @@
   <dimension ref="A3:D53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -33412,13 +33000,13 @@
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="7">
         <v>485.779111</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="7">
         <v>174.12032300000001</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="7">
         <v>329.94971700000002</v>
       </c>
     </row>
@@ -33426,13 +33014,13 @@
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="7">
         <v>403.32869599999998</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="7">
         <v>149.68</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="7">
         <v>276.50434799999999</v>
       </c>
     </row>
@@ -33440,13 +33028,13 @@
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="7">
         <v>534.26833299999998</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="7">
         <v>176.42500000000001</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="7">
         <v>355.34666649999997</v>
       </c>
     </row>
@@ -33454,13 +33042,13 @@
       <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="7">
         <v>461.80428599999999</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="7">
         <v>175.02676500000001</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="7">
         <v>318.4155255</v>
       </c>
     </row>
@@ -33468,13 +33056,13 @@
       <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="7">
         <v>369.8365</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="7">
         <v>172.429778</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="7">
         <v>271.13313900000003</v>
       </c>
     </row>
@@ -33482,13 +33070,13 @@
       <c r="A10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="7">
         <v>527.44687499999998</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="7">
         <v>176.245</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="7">
         <v>351.84593749999999</v>
       </c>
     </row>
@@ -33496,13 +33084,13 @@
       <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="7">
         <v>592.91671899999994</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="7">
         <v>181.874865</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="7">
         <v>387.39579199999997</v>
       </c>
     </row>
@@ -33510,13 +33098,13 @@
       <c r="A12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="7">
         <v>467.24244399999998</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="7">
         <v>160.501724</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="7">
         <v>313.87208399999997</v>
       </c>
     </row>
@@ -33524,13 +33112,13 @@
       <c r="A13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>458.20574099999999</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="7">
         <v>174.47388900000001</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="7">
         <v>316.33981499999999</v>
       </c>
     </row>
@@ -33538,13 +33126,13 @@
       <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="7">
         <v>592.91671899999994</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="7">
         <v>182.109318</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="7">
         <v>387.51301849999999</v>
       </c>
     </row>
@@ -33552,13 +33140,13 @@
       <c r="A15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="7">
         <v>473.069706</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="7">
         <v>166.27816300000001</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="7">
         <v>319.67393449999997</v>
       </c>
     </row>
@@ -33566,13 +33154,13 @@
       <c r="A16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="7">
         <v>496.08523400000001</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="7">
         <v>174.42400000000001</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="7">
         <v>335.254617</v>
       </c>
     </row>
@@ -33580,13 +33168,13 @@
       <c r="A17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="7">
         <v>511.36585400000001</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="7">
         <v>186.397368</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="7">
         <v>348.88161100000002</v>
       </c>
     </row>
@@ -33594,13 +33182,13 @@
       <c r="A18" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="7">
         <v>473.069706</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="7">
         <v>168.24645799999999</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="7">
         <v>320.65808199999998</v>
       </c>
     </row>
@@ -33608,13 +33196,13 @@
       <c r="A19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>407.74940299999997</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="7">
         <v>175.91054099999999</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="7">
         <v>291.829972</v>
       </c>
     </row>
@@ -33622,13 +33210,13 @@
       <c r="A20" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="7">
         <v>461.70246800000001</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="7">
         <v>181.19018199999999</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="7">
         <v>321.446325</v>
       </c>
     </row>
@@ -33636,13 +33224,13 @@
       <c r="A21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="7">
         <v>447.19237299999998</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="7">
         <v>176.502917</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="7">
         <v>311.847645</v>
       </c>
     </row>
@@ -33650,13 +33238,13 @@
       <c r="A22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="7">
         <v>407.74940299999997</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="7">
         <v>173.17078900000001</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="7">
         <v>290.46009600000002</v>
       </c>
     </row>
@@ -33664,13 +33252,13 @@
       <c r="A23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="7">
         <v>389.19027</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="7">
         <v>177.93424999999999</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="7">
         <v>283.56225999999998</v>
       </c>
     </row>
@@ -33678,13 +33266,13 @@
       <c r="A24" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="7">
         <v>448.32955099999998</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="7">
         <v>168.322439</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="7">
         <v>308.32599499999998</v>
       </c>
     </row>
@@ -33692,13 +33280,13 @@
       <c r="A25" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="7">
         <v>432.17500000000001</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="7">
         <v>188.25</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="7">
         <v>310.21249999999998</v>
       </c>
     </row>
@@ -33706,13 +33294,13 @@
       <c r="A26" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="7">
         <v>383.29708299999999</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="7">
         <v>177.93424999999999</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="7">
         <v>280.61566649999997</v>
       </c>
     </row>
@@ -33720,13 +33308,13 @@
       <c r="A27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="7">
         <v>500.42761200000001</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="7">
         <v>190.317407</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="7">
         <v>345.37250949999998</v>
       </c>
     </row>
@@ -33734,13 +33322,13 @@
       <c r="A28" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="7">
         <v>421.22607099999999</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="7">
         <v>169.37855300000001</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="7">
         <v>295.30231200000003</v>
       </c>
     </row>
@@ -33748,13 +33336,13 @@
       <c r="A29" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="7">
         <v>435.04548999999997</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="7">
         <v>185.66218799999999</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="7">
         <v>310.35383899999999</v>
       </c>
     </row>
@@ -33762,13 +33350,13 @@
       <c r="A30" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="7">
         <v>503.352754</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="7">
         <v>190.317407</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="7">
         <v>346.8350805</v>
       </c>
     </row>
@@ -33776,13 +33364,13 @@
       <c r="A31" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="7">
         <v>503.88014900000002</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="7">
         <v>170.47483299999999</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="7">
         <v>337.17749100000003</v>
       </c>
     </row>
@@ -33790,13 +33378,13 @@
       <c r="A32" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="7">
         <v>560.44280000000003</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="7">
         <v>176.442857</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="7">
         <v>368.44282850000002</v>
       </c>
     </row>
@@ -33804,13 +33392,13 @@
       <c r="A33" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="7">
         <v>496.02258599999999</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="7">
         <v>184.76482799999999</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="7">
         <v>340.39370700000001</v>
       </c>
     </row>
@@ -33818,13 +33406,13 @@
       <c r="A34" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="7">
         <v>503.88014900000002</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="7">
         <v>170.47483299999999</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="7">
         <v>337.17749100000003</v>
       </c>
     </row>
@@ -33832,13 +33420,13 @@
       <c r="A35" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="7">
         <v>381.55712599999998</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="7">
         <v>168.062286</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="7">
         <v>274.80970600000001</v>
       </c>
     </row>
@@ -33846,13 +33434,13 @@
       <c r="A36" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="7">
         <v>523.20617400000003</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="7">
         <v>167.392157</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="7">
         <v>345.29916550000002</v>
       </c>
     </row>
@@ -33860,13 +33448,13 @@
       <c r="A37" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="7">
         <v>478.120698</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="7">
         <v>189.32054099999999</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="7">
         <v>333.7206195</v>
       </c>
     </row>
@@ -33874,13 +33462,13 @@
       <c r="A38" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="7">
         <v>388.826235</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="7">
         <v>168.88058000000001</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="7">
         <v>278.8534075</v>
       </c>
     </row>
@@ -33888,13 +33476,13 @@
       <c r="A39" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="7">
         <v>401.36260299999998</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="7">
         <v>169.63716700000001</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="7">
         <v>285.49988500000001</v>
       </c>
     </row>
@@ -33902,13 +33490,13 @@
       <c r="A40" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="7">
         <v>448.87352499999997</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="7">
         <v>167.09899999999999</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="7">
         <v>307.98626249999995</v>
       </c>
     </row>
@@ -33916,13 +33504,13 @@
       <c r="A41" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="7">
         <v>649.76898000000006</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="7">
         <v>182.418125</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="7">
         <v>416.09355250000004</v>
       </c>
     </row>
@@ -33930,13 +33518,13 @@
       <c r="A42" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="7">
         <v>392.59613300000001</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="7">
         <v>168.68573799999999</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="7">
         <v>280.64093550000001</v>
       </c>
     </row>
@@ -33944,13 +33532,13 @@
       <c r="A43" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="7">
         <v>420.28942899999998</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="7">
         <v>159.28303600000001</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="7">
         <v>289.78623249999998</v>
       </c>
     </row>
@@ -33958,13 +33546,13 @@
       <c r="A44" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="7">
         <v>448.88338499999998</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="7">
         <v>167.507835</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="7">
         <v>308.19560999999999</v>
       </c>
     </row>
@@ -33972,13 +33560,13 @@
       <c r="A45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="7">
         <v>479.810857</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="7">
         <v>191.736875</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="7">
         <v>335.773866</v>
       </c>
     </row>
@@ -33986,13 +33574,13 @@
       <c r="A46" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="7">
         <v>420.28942899999998</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="7">
         <v>160.73166699999999</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="7">
         <v>290.51054799999997</v>
       </c>
     </row>
@@ -34000,13 +33588,13 @@
       <c r="A47" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="7">
         <v>441.81304899999998</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="7">
         <v>173.33709099999999</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="7">
         <v>307.57506999999998</v>
       </c>
     </row>
@@ -34014,13 +33602,13 @@
       <c r="A48" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="7">
         <v>415.375472</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="7">
         <v>165.32224500000001</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="7">
         <v>290.34885850000001</v>
       </c>
     </row>
@@ -34028,13 +33616,13 @@
       <c r="A49" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="7">
         <v>480.16156899999999</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="7">
         <v>176.672821</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="7">
         <v>328.41719499999999</v>
       </c>
     </row>
@@ -34042,13 +33630,13 @@
       <c r="A50" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="7">
         <v>441.81304899999998</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="7">
         <v>171.47157899999999</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="7">
         <v>306.642314</v>
       </c>
     </row>
@@ -34056,13 +33644,13 @@
       <c r="A51" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="7">
         <v>403.32869599999998</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="7">
         <v>149.68</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="7">
         <v>276.50434799999999</v>
       </c>
     </row>
@@ -34070,13 +33658,13 @@
       <c r="A52" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="7">
         <v>566.74575800000002</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="7">
         <v>159.87581800000001</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="7">
         <v>363.310788</v>
       </c>
     </row>
@@ -34084,13 +33672,13 @@
       <c r="A53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="7">
         <v>465.24627610416672</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="7">
         <v>173.59157262500005</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="7">
         <v>319.41892436458335</v>
       </c>
     </row>
